--- a/KoF/GPS-Speedsurfing-Users.xlsx
+++ b/KoF/GPS-Speedsurfing-Users.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\KoF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F1169F-48FE-41CE-B028-5D63C4F0E62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D82DDD3-64DA-4BC0-91B2-AD33CDAC2856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="BaseUrl" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">User!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">User!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
   <si>
     <t>BQ</t>
   </si>
@@ -282,9 +282,6 @@
     <t>Millbergs</t>
   </si>
   <si>
-    <t>Frasse</t>
-  </si>
-  <si>
     <t>E Larsson</t>
   </si>
   <si>
@@ -325,6 +322,27 @@
   </si>
   <si>
     <t>M Dahlberg</t>
+  </si>
+  <si>
+    <t>Plettil</t>
+  </si>
+  <si>
+    <t>Dylan de Jong</t>
+  </si>
+  <si>
+    <t>djong1</t>
+  </si>
+  <si>
+    <t>Sebastian Thoem</t>
+  </si>
+  <si>
+    <t>Bastian</t>
+  </si>
+  <si>
+    <t>Henke Torslanda</t>
+  </si>
+  <si>
+    <t>Henrik Larsson</t>
   </si>
 </sst>
 </file>
@@ -386,12 +404,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -435,10 +459,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -722,20 +749,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L50"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.77734375" customWidth="1"/>
-    <col min="8" max="8" width="44.21875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="58.109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="56.109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="8.88671875" collapsed="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="44.33203125" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="58.109375" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="56.109375" customWidth="1" outlineLevel="1"/>
     <col min="13" max="13" width="48.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -752,19 +779,19 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>68</v>
       </c>
       <c r="J1" t="s">
@@ -785,15 +812,15 @@
         <v>2558</v>
       </c>
       <c r="E2" s="7" t="str">
-        <f>IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(H2,D2),IF(B2="",C2,B2)),"")</f>
+        <f t="shared" ref="E2:E22" si="0">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(H2,D2),IF(B2="",C2,B2)),"")</f>
         <v>BQ</v>
       </c>
       <c r="F2" s="7" t="str">
-        <f>IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(I2,D2),IF(B2="",C2,B2)),"")</f>
+        <f t="shared" ref="F2:F22" si="1">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(I2,D2),IF(B2="",C2,B2)),"")</f>
         <v>BQ</v>
       </c>
       <c r="G2" s="7" t="str">
-        <f>IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(J2,D2),IF(B2="",C2,B2)),"")</f>
+        <f t="shared" ref="G2:G22" si="2">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(J2,D2),IF(B2="",C2,B2)),"")</f>
         <v>BQ</v>
       </c>
       <c r="H2" s="4" t="str">
@@ -825,15 +852,15 @@
         <v>25610</v>
       </c>
       <c r="E3" s="7" t="str">
-        <f>IF(D3&gt;0,HYPERLINK(_xlfn.CONCAT(H3,D3),IF(B3="",C3,B3)),"")</f>
+        <f t="shared" si="0"/>
         <v>AN</v>
       </c>
       <c r="F3" s="7" t="str">
-        <f>IF(D3&gt;0,HYPERLINK(_xlfn.CONCAT(I3,D3),IF(B3="",C3,B3)),"")</f>
+        <f t="shared" si="1"/>
         <v>AN</v>
       </c>
       <c r="G3" s="7" t="str">
-        <f>IF(D3&gt;0,HYPERLINK(_xlfn.CONCAT(J3,D3),IF(B3="",C3,B3)),"")</f>
+        <f t="shared" si="2"/>
         <v>AN</v>
       </c>
       <c r="H3" s="4" t="str">
@@ -858,22 +885,22 @@
       <c r="B4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="4">
         <v>497225</v>
       </c>
       <c r="E4" s="7" t="str">
-        <f>IF(D4&gt;0,HYPERLINK(_xlfn.CONCAT(H4,D4),IF(B4="",C4,B4)),"")</f>
+        <f t="shared" si="0"/>
         <v>Arne</v>
       </c>
       <c r="F4" s="7" t="str">
-        <f>IF(D4&gt;0,HYPERLINK(_xlfn.CONCAT(I4,D4),IF(B4="",C4,B4)),"")</f>
+        <f t="shared" si="1"/>
         <v>Arne</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f>IF(D4&gt;0,HYPERLINK(_xlfn.CONCAT(J4,D4),IF(B4="",C4,B4)),"")</f>
+        <f t="shared" si="2"/>
         <v>Arne</v>
       </c>
       <c r="H4" s="4" t="str">
@@ -896,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>25</v>
@@ -905,15 +932,15 @@
         <v>469015</v>
       </c>
       <c r="E5" s="7" t="str">
-        <f>IF(D5&gt;0,HYPERLINK(_xlfn.CONCAT(H5,D5),IF(B5="",C5,B5)),"")</f>
+        <f t="shared" si="0"/>
         <v>AT</v>
       </c>
       <c r="F5" s="7" t="str">
-        <f>IF(D5&gt;0,HYPERLINK(_xlfn.CONCAT(I5,D5),IF(B5="",C5,B5)),"")</f>
+        <f t="shared" si="1"/>
         <v>AT</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f>IF(D5&gt;0,HYPERLINK(_xlfn.CONCAT(J5,D5),IF(B5="",C5,B5)),"")</f>
+        <f t="shared" si="2"/>
         <v>AT</v>
       </c>
       <c r="H5" s="4" t="str">
@@ -945,15 +972,15 @@
         <v>22378</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f>IF(D6&gt;0,HYPERLINK(_xlfn.CONCAT(H6,D6),IF(B6="",C6,B6)),"")</f>
+        <f t="shared" si="0"/>
         <v>J&amp;B</v>
       </c>
       <c r="F6" s="7" t="str">
-        <f>IF(D6&gt;0,HYPERLINK(_xlfn.CONCAT(I6,D6),IF(B6="",C6,B6)),"")</f>
+        <f t="shared" si="1"/>
         <v>J&amp;B</v>
       </c>
       <c r="G6" s="7" t="str">
-        <f>IF(D6&gt;0,HYPERLINK(_xlfn.CONCAT(J6,D6),IF(B6="",C6,B6)),"")</f>
+        <f t="shared" si="2"/>
         <v>J&amp;B</v>
       </c>
       <c r="H6" s="4" t="str">
@@ -978,22 +1005,22 @@
       <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="4">
         <v>23841</v>
       </c>
       <c r="E7" s="7" t="str">
-        <f>IF(D7&gt;0,HYPERLINK(_xlfn.CONCAT(H7,D7),IF(B7="",C7,B7)),"")</f>
+        <f t="shared" si="0"/>
         <v>Berra</v>
       </c>
       <c r="F7" s="7" t="str">
-        <f>IF(D7&gt;0,HYPERLINK(_xlfn.CONCAT(I7,D7),IF(B7="",C7,B7)),"")</f>
+        <f t="shared" si="1"/>
         <v>Berra</v>
       </c>
       <c r="G7" s="7" t="str">
-        <f>IF(D7&gt;0,HYPERLINK(_xlfn.CONCAT(J7,D7),IF(B7="",C7,B7)),"")</f>
+        <f t="shared" si="2"/>
         <v>Berra</v>
       </c>
       <c r="H7" s="4" t="str">
@@ -1021,15 +1048,15 @@
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="7" t="str">
-        <f>IF(D8&gt;0,HYPERLINK(_xlfn.CONCAT(H8,D8),IF(B8="",C8,B8)),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F8" s="7" t="str">
-        <f>IF(D8&gt;0,HYPERLINK(_xlfn.CONCAT(I8,D8),IF(B8="",C8,B8)),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G8" s="7" t="str">
-        <f>IF(D8&gt;0,HYPERLINK(_xlfn.CONCAT(J8,D8),IF(B8="",C8,B8)),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="H8" s="4" t="str">
@@ -1057,15 +1084,15 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="7" t="str">
-        <f>IF(D9&gt;0,HYPERLINK(_xlfn.CONCAT(H9,D9),IF(B9="",C9,B9)),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F9" s="7" t="str">
-        <f>IF(D9&gt;0,HYPERLINK(_xlfn.CONCAT(I9,D9),IF(B9="",C9,B9)),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G9" s="7" t="str">
-        <f>IF(D9&gt;0,HYPERLINK(_xlfn.CONCAT(J9,D9),IF(B9="",C9,B9)),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="H9" s="4" t="str">
@@ -1093,18 +1120,20 @@
       <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>587</v>
+      </c>
       <c r="E10" s="7" t="str">
-        <f>IF(D10&gt;0,HYPERLINK(_xlfn.CONCAT(H10,D10),IF(B10="",C10,B10)),"")</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>Borgelind</v>
       </c>
       <c r="F10" s="7" t="str">
-        <f>IF(D10&gt;0,HYPERLINK(_xlfn.CONCAT(I10,D10),IF(B10="",C10,B10)),"")</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Borgelind</v>
       </c>
       <c r="G10" s="7" t="str">
-        <f>IF(D10&gt;0,HYPERLINK(_xlfn.CONCAT(J10,D10),IF(B10="",C10,B10)),"")</f>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Borgelind</v>
       </c>
       <c r="H10" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1128,22 +1157,22 @@
       <c r="B11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="4">
         <v>4051</v>
       </c>
       <c r="E11" s="7" t="str">
-        <f>IF(D11&gt;0,HYPERLINK(_xlfn.CONCAT(H11,D11),IF(B11="",C11,B11)),"")</f>
+        <f t="shared" si="0"/>
         <v>EA</v>
       </c>
       <c r="F11" s="7" t="str">
-        <f>IF(D11&gt;0,HYPERLINK(_xlfn.CONCAT(I11,D11),IF(B11="",C11,B11)),"")</f>
+        <f t="shared" si="1"/>
         <v>EA</v>
       </c>
       <c r="G11" s="7" t="str">
-        <f>IF(D11&gt;0,HYPERLINK(_xlfn.CONCAT(J11,D11),IF(B11="",C11,B11)),"")</f>
+        <f t="shared" si="2"/>
         <v>EA</v>
       </c>
       <c r="H11" s="4" t="str">
@@ -1175,15 +1204,15 @@
         <v>27753</v>
       </c>
       <c r="E12" s="7" t="str">
-        <f>IF(D12&gt;0,HYPERLINK(_xlfn.CONCAT(H12,D12),IF(B12="",C12,B12)),"")</f>
+        <f t="shared" si="0"/>
         <v>Grimberg</v>
       </c>
       <c r="F12" s="7" t="str">
-        <f>IF(D12&gt;0,HYPERLINK(_xlfn.CONCAT(I12,D12),IF(B12="",C12,B12)),"")</f>
+        <f t="shared" si="1"/>
         <v>Grimberg</v>
       </c>
       <c r="G12" s="7" t="str">
-        <f>IF(D12&gt;0,HYPERLINK(_xlfn.CONCAT(J12,D12),IF(B12="",C12,B12)),"")</f>
+        <f t="shared" si="2"/>
         <v>Grimberg</v>
       </c>
       <c r="H12" s="4" t="str">
@@ -1211,15 +1240,15 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="7" t="str">
-        <f>IF(D13&gt;0,HYPERLINK(_xlfn.CONCAT(H13,D13),IF(B13="",C13,B13)),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F13" s="7" t="str">
-        <f>IF(D13&gt;0,HYPERLINK(_xlfn.CONCAT(I13,D13),IF(B13="",C13,B13)),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G13" s="7" t="str">
-        <f>IF(D13&gt;0,HYPERLINK(_xlfn.CONCAT(J13,D13),IF(B13="",C13,B13)),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="H13" s="4" t="str">
@@ -1244,22 +1273,22 @@
       <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="4">
         <v>1007</v>
       </c>
       <c r="E14" s="7" t="str">
-        <f>IF(D14&gt;0,HYPERLINK(_xlfn.CONCAT(H14,D14),IF(B14="",C14,B14)),"")</f>
+        <f t="shared" si="0"/>
         <v>Budda</v>
       </c>
       <c r="F14" s="7" t="str">
-        <f>IF(D14&gt;0,HYPERLINK(_xlfn.CONCAT(I14,D14),IF(B14="",C14,B14)),"")</f>
+        <f t="shared" si="1"/>
         <v>Budda</v>
       </c>
       <c r="G14" s="7" t="str">
-        <f>IF(D14&gt;0,HYPERLINK(_xlfn.CONCAT(J14,D14),IF(B14="",C14,B14)),"")</f>
+        <f t="shared" si="2"/>
         <v>Budda</v>
       </c>
       <c r="H14" s="4" t="str">
@@ -1287,15 +1316,15 @@
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="7" t="str">
-        <f>IF(D15&gt;0,HYPERLINK(_xlfn.CONCAT(H15,D15),IF(B15="",C15,B15)),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F15" s="7" t="str">
-        <f>IF(D15&gt;0,HYPERLINK(_xlfn.CONCAT(I15,D15),IF(B15="",C15,B15)),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G15" s="7" t="str">
-        <f>IF(D15&gt;0,HYPERLINK(_xlfn.CONCAT(J15,D15),IF(B15="",C15,B15)),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="H15" s="4" t="str">
@@ -1318,25 +1347,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4">
-        <v>713</v>
+        <v>53</v>
       </c>
       <c r="E16" s="7" t="str">
-        <f>IF(D16&gt;0,HYPERLINK(_xlfn.CONCAT(H16,D16),IF(B16="",C16,B16)),"")</f>
-        <v>E Larsson</v>
+        <f t="shared" si="0"/>
+        <v>djong1</v>
       </c>
       <c r="F16" s="7" t="str">
-        <f>IF(D16&gt;0,HYPERLINK(_xlfn.CONCAT(I16,D16),IF(B16="",C16,B16)),"")</f>
-        <v>E Larsson</v>
+        <f t="shared" si="1"/>
+        <v>djong1</v>
       </c>
       <c r="G16" s="7" t="str">
-        <f>IF(D16&gt;0,HYPERLINK(_xlfn.CONCAT(J16,D16),IF(B16="",C16,B16)),"")</f>
-        <v>E Larsson</v>
+        <f t="shared" si="2"/>
+        <v>djong1</v>
       </c>
       <c r="H16" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1358,23 +1387,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="D17" s="4">
+        <v>713</v>
+      </c>
       <c r="E17" s="7" t="str">
-        <f>IF(D17&gt;0,HYPERLINK(_xlfn.CONCAT(H17,D17),IF(B17="",C17,B17)),"")</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>E Larsson</v>
       </c>
       <c r="F17" s="7" t="str">
-        <f>IF(D17&gt;0,HYPERLINK(_xlfn.CONCAT(I17,D17),IF(B17="",C17,B17)),"")</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>E Larsson</v>
       </c>
       <c r="G17" s="7" t="str">
-        <f>IF(D17&gt;0,HYPERLINK(_xlfn.CONCAT(J17,D17),IF(B17="",C17,B17)),"")</f>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>E Larsson</v>
       </c>
       <c r="H17" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1396,25 +1427,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="4">
-        <v>483960</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="7" t="str">
-        <f>IF(D18&gt;0,HYPERLINK(_xlfn.CONCAT(H18,D18),IF(B18="",C18,B18)),"")</f>
-        <v>Frasse</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="F18" s="7" t="str">
-        <f>IF(D18&gt;0,HYPERLINK(_xlfn.CONCAT(I18,D18),IF(B18="",C18,B18)),"")</f>
-        <v>Frasse</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="G18" s="7" t="str">
-        <f>IF(D18&gt;0,HYPERLINK(_xlfn.CONCAT(J18,D18),IF(B18="",C18,B18)),"")</f>
-        <v>Frasse</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H18" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1435,22 +1464,26 @@
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="4"/>
+      <c r="B19" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="4">
+        <v>18200</v>
+      </c>
       <c r="E19" s="7" t="str">
-        <f>IF(D19&gt;0,HYPERLINK(_xlfn.CONCAT(H19,D19),IF(B19="",C19,B19)),"")</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>Plettil</v>
       </c>
       <c r="F19" s="7" t="str">
-        <f>IF(D19&gt;0,HYPERLINK(_xlfn.CONCAT(I19,D19),IF(B19="",C19,B19)),"")</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Plettil</v>
       </c>
       <c r="G19" s="7" t="str">
-        <f>IF(D19&gt;0,HYPERLINK(_xlfn.CONCAT(J19,D19),IF(B19="",C19,B19)),"")</f>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Plettil</v>
       </c>
       <c r="H19" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1471,26 +1504,22 @@
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="B20" s="6"/>
       <c r="C20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="4">
-        <v>26470</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="7" t="str">
-        <f>IF(D20&gt;0,HYPERLINK(_xlfn.CONCAT(H20,D20),IF(B20="",C20,B20)),"")</f>
-        <v>Harald</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="F20" s="7" t="str">
-        <f>IF(D20&gt;0,HYPERLINK(_xlfn.CONCAT(I20,D20),IF(B20="",C20,B20)),"")</f>
-        <v>Harald</v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="G20" s="7" t="str">
-        <f>IF(D20&gt;0,HYPERLINK(_xlfn.CONCAT(J20,D20),IF(B20="",C20,B20)),"")</f>
-        <v>Harald</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="H20" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1511,22 +1540,26 @@
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="D21" s="4">
+        <v>26470</v>
+      </c>
       <c r="E21" s="7" t="str">
-        <f>IF(D21&gt;0,HYPERLINK(_xlfn.CONCAT(H21,D21),IF(B21="",C21,B21)),"")</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>Harald</v>
       </c>
       <c r="F21" s="7" t="str">
-        <f>IF(D21&gt;0,HYPERLINK(_xlfn.CONCAT(I21,D21),IF(B21="",C21,B21)),"")</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>Harald</v>
       </c>
       <c r="G21" s="7" t="str">
-        <f>IF(D21&gt;0,HYPERLINK(_xlfn.CONCAT(J21,D21),IF(B21="",C21,B21)),"")</f>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Harald</v>
       </c>
       <c r="H21" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1544,29 +1577,27 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
+      <c r="A22" s="4"/>
       <c r="B22" s="6" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="D22" s="4">
-        <v>495257</v>
+        <v>27859</v>
       </c>
       <c r="E22" s="7" t="str">
-        <f>IF(D22&gt;0,HYPERLINK(_xlfn.CONCAT(H22,D22),IF(B22="",C22,B22)),"")</f>
-        <v>JesPer</v>
+        <f t="shared" si="0"/>
+        <v>Henke Torslanda</v>
       </c>
       <c r="F22" s="7" t="str">
-        <f>IF(D22&gt;0,HYPERLINK(_xlfn.CONCAT(I22,D22),IF(B22="",C22,B22)),"")</f>
-        <v>JesPer</v>
+        <f t="shared" si="1"/>
+        <v>Henke Torslanda</v>
       </c>
       <c r="G22" s="7" t="str">
-        <f>IF(D22&gt;0,HYPERLINK(_xlfn.CONCAT(J22,D22),IF(B22="",C22,B22)),"")</f>
-        <v>JesPer</v>
+        <f t="shared" si="2"/>
+        <v>Henke Torslanda</v>
       </c>
       <c r="H22" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1585,28 +1616,24 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B23" s="6"/>
       <c r="C23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="4">
-        <v>26191</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D23" s="4"/>
       <c r="E23" s="7" t="str">
-        <f>IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(H23,D23),IF(B23="",C23,B23)),"")</f>
-        <v>Jocke</v>
+        <f t="shared" ref="E23:E49" si="3">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(H23,D23),IF(B23="",C23,B23)),"")</f>
+        <v/>
       </c>
       <c r="F23" s="7" t="str">
-        <f>IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(I23,D23),IF(B23="",C23,B23)),"")</f>
-        <v>Jocke</v>
+        <f t="shared" ref="F23:F49" si="4">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(I23,D23),IF(B23="",C23,B23)),"")</f>
+        <v/>
       </c>
       <c r="G23" s="7" t="str">
-        <f>IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(J23,D23),IF(B23="",C23,B23)),"")</f>
-        <v>Jocke</v>
+        <f t="shared" ref="G23:G49" si="5">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(J23,D23),IF(B23="",C23,B23)),"")</f>
+        <v/>
       </c>
       <c r="H23" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1625,26 +1652,28 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="5" t="s">
-        <v>41</v>
+        <v>22</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D24" s="4">
-        <v>604</v>
+        <v>495257</v>
       </c>
       <c r="E24" s="7" t="str">
-        <f>IF(D24&gt;0,HYPERLINK(_xlfn.CONCAT(H24,D24),IF(B24="",C24,B24)),"")</f>
-        <v>Johan Gelander</v>
+        <f t="shared" si="3"/>
+        <v>JesPer</v>
       </c>
       <c r="F24" s="7" t="str">
-        <f>IF(D24&gt;0,HYPERLINK(_xlfn.CONCAT(I24,D24),IF(B24="",C24,B24)),"")</f>
-        <v>Johan Gelander</v>
+        <f t="shared" si="4"/>
+        <v>JesPer</v>
       </c>
       <c r="G24" s="7" t="str">
-        <f>IF(D24&gt;0,HYPERLINK(_xlfn.CONCAT(J24,D24),IF(B24="",C24,B24)),"")</f>
-        <v>Johan Gelander</v>
+        <f t="shared" si="5"/>
+        <v>JesPer</v>
       </c>
       <c r="H24" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1663,28 +1692,28 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" s="4">
-        <v>470910</v>
+        <v>26191</v>
       </c>
       <c r="E25" s="7" t="str">
-        <f>IF(D25&gt;0,HYPERLINK(_xlfn.CONCAT(H25,D25),IF(B25="",C25,B25)),"")</f>
-        <v>Millbergs</v>
+        <f t="shared" si="3"/>
+        <v>Jocke</v>
       </c>
       <c r="F25" s="7" t="str">
-        <f>IF(D25&gt;0,HYPERLINK(_xlfn.CONCAT(I25,D25),IF(B25="",C25,B25)),"")</f>
-        <v>Millbergs</v>
+        <f t="shared" si="4"/>
+        <v>Jocke</v>
       </c>
       <c r="G25" s="7" t="str">
-        <f>IF(D25&gt;0,HYPERLINK(_xlfn.CONCAT(J25,D25),IF(B25="",C25,B25)),"")</f>
-        <v>Millbergs</v>
+        <f t="shared" si="5"/>
+        <v>Jocke</v>
       </c>
       <c r="H25" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1703,28 +1732,26 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D26" s="4">
-        <v>6195</v>
+        <v>604</v>
       </c>
       <c r="E26" s="7" t="str">
-        <f>IF(D26&gt;0,HYPERLINK(_xlfn.CONCAT(H26,D26),IF(B26="",C26,B26)),"")</f>
-        <v>Joko</v>
+        <f t="shared" si="3"/>
+        <v>Johan Gelander</v>
       </c>
       <c r="F26" s="7" t="str">
-        <f>IF(D26&gt;0,HYPERLINK(_xlfn.CONCAT(I26,D26),IF(B26="",C26,B26)),"")</f>
-        <v>Joko</v>
+        <f t="shared" si="4"/>
+        <v>Johan Gelander</v>
       </c>
       <c r="G26" s="7" t="str">
-        <f>IF(D26&gt;0,HYPERLINK(_xlfn.CONCAT(J26,D26),IF(B26="",C26,B26)),"")</f>
-        <v>Joko</v>
+        <f t="shared" si="5"/>
+        <v>Johan Gelander</v>
       </c>
       <c r="H26" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1743,28 +1770,28 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D27" s="4">
-        <v>469112</v>
+        <v>470910</v>
       </c>
       <c r="E27" s="7" t="str">
-        <f>IF(D27&gt;0,HYPERLINK(_xlfn.CONCAT(H27,D27),IF(B27="",C27,B27)),"")</f>
-        <v>Bergström</v>
+        <f t="shared" si="3"/>
+        <v>Millbergs</v>
       </c>
       <c r="F27" s="7" t="str">
-        <f>IF(D27&gt;0,HYPERLINK(_xlfn.CONCAT(I27,D27),IF(B27="",C27,B27)),"")</f>
-        <v>Bergström</v>
+        <f t="shared" si="4"/>
+        <v>Millbergs</v>
       </c>
       <c r="G27" s="7" t="str">
-        <f>IF(D27&gt;0,HYPERLINK(_xlfn.CONCAT(J27,D27),IF(B27="",C27,B27)),"")</f>
-        <v>Bergström</v>
+        <f t="shared" si="5"/>
+        <v>Millbergs</v>
       </c>
       <c r="H27" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1783,28 +1810,28 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D28" s="4">
-        <v>26663</v>
+        <v>6195</v>
       </c>
       <c r="E28" s="7" t="str">
-        <f>IF(D28&gt;0,HYPERLINK(_xlfn.CONCAT(H28,D28),IF(B28="",C28,B28)),"")</f>
-        <v>Göran</v>
+        <f t="shared" si="3"/>
+        <v>Joko</v>
       </c>
       <c r="F28" s="7" t="str">
-        <f>IF(D28&gt;0,HYPERLINK(_xlfn.CONCAT(I28,D28),IF(B28="",C28,B28)),"")</f>
-        <v>Göran</v>
+        <f t="shared" si="4"/>
+        <v>Joko</v>
       </c>
       <c r="G28" s="7" t="str">
-        <f>IF(D28&gt;0,HYPERLINK(_xlfn.CONCAT(J28,D28),IF(B28="",C28,B28)),"")</f>
-        <v>Göran</v>
+        <f t="shared" si="5"/>
+        <v>Joko</v>
       </c>
       <c r="H28" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1823,28 +1850,28 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29" s="4">
-        <v>494504</v>
+        <v>469112</v>
       </c>
       <c r="E29" s="7" t="str">
-        <f>IF(D29&gt;0,HYPERLINK(_xlfn.CONCAT(H29,D29),IF(B29="",C29,B29)),"")</f>
-        <v>Sören</v>
+        <f t="shared" si="3"/>
+        <v>Bergström</v>
       </c>
       <c r="F29" s="7" t="str">
-        <f>IF(D29&gt;0,HYPERLINK(_xlfn.CONCAT(I29,D29),IF(B29="",C29,B29)),"")</f>
-        <v>Sören</v>
+        <f t="shared" si="4"/>
+        <v>Bergström</v>
       </c>
       <c r="G29" s="7" t="str">
-        <f>IF(D29&gt;0,HYPERLINK(_xlfn.CONCAT(J29,D29),IF(B29="",C29,B29)),"")</f>
-        <v>Sören</v>
+        <f t="shared" si="5"/>
+        <v>Bergström</v>
       </c>
       <c r="H29" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1863,28 +1890,28 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>47</v>
+        <v>85</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D30" s="4">
-        <v>469141</v>
+        <v>26663</v>
       </c>
       <c r="E30" s="7" t="str">
-        <f>IF(D30&gt;0,HYPERLINK(_xlfn.CONCAT(H30,D30),IF(B30="",C30,B30)),"")</f>
-        <v>Kate</v>
+        <f t="shared" si="3"/>
+        <v>Göran</v>
       </c>
       <c r="F30" s="7" t="str">
-        <f>IF(D30&gt;0,HYPERLINK(_xlfn.CONCAT(I30,D30),IF(B30="",C30,B30)),"")</f>
-        <v>Kate</v>
+        <f t="shared" si="4"/>
+        <v>Göran</v>
       </c>
       <c r="G30" s="7" t="str">
-        <f>IF(D30&gt;0,HYPERLINK(_xlfn.CONCAT(J30,D30),IF(B30="",C30,B30)),"")</f>
-        <v>Kate</v>
+        <f t="shared" si="5"/>
+        <v>Göran</v>
       </c>
       <c r="H30" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1903,26 +1930,28 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="D31" s="4">
+        <v>494504</v>
+      </c>
       <c r="E31" s="7" t="str">
-        <f>IF(D31&gt;0,HYPERLINK(_xlfn.CONCAT(H31,D31),IF(B31="",C31,B31)),"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>Sören</v>
       </c>
       <c r="F31" s="7" t="str">
-        <f>IF(D31&gt;0,HYPERLINK(_xlfn.CONCAT(I31,D31),IF(B31="",C31,B31)),"")</f>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>Sören</v>
       </c>
       <c r="G31" s="7" t="str">
-        <f>IF(D31&gt;0,HYPERLINK(_xlfn.CONCAT(J31,D31),IF(B31="",C31,B31)),"")</f>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>Sören</v>
       </c>
       <c r="H31" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1941,28 +1970,28 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D32" s="4">
-        <v>2250</v>
+        <v>469141</v>
       </c>
       <c r="E32" s="7" t="str">
-        <f>IF(D32&gt;0,HYPERLINK(_xlfn.CONCAT(H32,D32),IF(B32="",C32,B32)),"")</f>
-        <v>Richardsson</v>
+        <f t="shared" si="3"/>
+        <v>Kate</v>
       </c>
       <c r="F32" s="7" t="str">
-        <f>IF(D32&gt;0,HYPERLINK(_xlfn.CONCAT(I32,D32),IF(B32="",C32,B32)),"")</f>
-        <v>Richardsson</v>
+        <f t="shared" si="4"/>
+        <v>Kate</v>
       </c>
       <c r="G32" s="7" t="str">
-        <f>IF(D32&gt;0,HYPERLINK(_xlfn.CONCAT(J32,D32),IF(B32="",C32,B32)),"")</f>
-        <v>Richardsson</v>
+        <f t="shared" si="5"/>
+        <v>Kate</v>
       </c>
       <c r="H32" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -1981,25 +2010,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="7" t="str">
-        <f>IF(D33&gt;0,HYPERLINK(_xlfn.CONCAT(H33,D33),IF(B33="",C33,B33)),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="F33" s="7" t="str">
-        <f>IF(D33&gt;0,HYPERLINK(_xlfn.CONCAT(I33,D33),IF(B33="",C33,B33)),"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G33" s="7" t="str">
-        <f>IF(D33&gt;0,HYPERLINK(_xlfn.CONCAT(J33,D33),IF(B33="",C33,B33)),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="H33" s="4" t="str">
@@ -2019,54 +2048,65 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="D34" s="4">
-        <v>48391</v>
+        <v>2250</v>
       </c>
       <c r="E34" s="7" t="str">
-        <f>IF(D34&gt;0,HYPERLINK(_xlfn.CONCAT(H34,D34),IF(B34="",C34,B34)),"")</f>
-        <v>Distner</v>
+        <f t="shared" si="3"/>
+        <v>Richardsson</v>
       </c>
       <c r="F34" s="7" t="str">
-        <f>IF(D34&gt;0,HYPERLINK(_xlfn.CONCAT(I34,D34),IF(B34="",C34,B34)),"")</f>
-        <v>Distner</v>
+        <f t="shared" si="4"/>
+        <v>Richardsson</v>
       </c>
       <c r="G34" s="7" t="str">
-        <f>IF(D34&gt;0,HYPERLINK(_xlfn.CONCAT(J34,D34),IF(B34="",C34,B34)),"")</f>
-        <v>Distner</v>
-      </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+        <f t="shared" si="5"/>
+        <v>Richardsson</v>
+      </c>
+      <c r="H34" s="4" t="str">
+        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+      </c>
+      <c r="I34" s="4" t="str">
+        <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="J34" s="4" t="str">
+        <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="C35" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="7" t="str">
-        <f>IF(D35&gt;0,HYPERLINK(_xlfn.CONCAT(H35,D35),IF(B35="",C35,B35)),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="F35" s="7" t="str">
-        <f>IF(D35&gt;0,HYPERLINK(_xlfn.CONCAT(I35,D35),IF(B35="",C35,B35)),"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G35" s="7" t="str">
-        <f>IF(D35&gt;0,HYPERLINK(_xlfn.CONCAT(J35,D35),IF(B35="",C35,B35)),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="H35" s="4" t="str">
@@ -2086,24 +2126,28 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="C36" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="D36" s="4">
+        <v>48391</v>
+      </c>
       <c r="E36" s="7" t="str">
-        <f>IF(D36&gt;0,HYPERLINK(_xlfn.CONCAT(H36,D36),IF(B36="",C36,B36)),"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>Distner</v>
       </c>
       <c r="F36" s="7" t="str">
-        <f>IF(D36&gt;0,HYPERLINK(_xlfn.CONCAT(I36,D36),IF(B36="",C36,B36)),"")</f>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>Distner</v>
       </c>
       <c r="G36" s="7" t="str">
-        <f>IF(D36&gt;0,HYPERLINK(_xlfn.CONCAT(J36,D36),IF(B36="",C36,B36)),"")</f>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>Distner</v>
       </c>
       <c r="H36" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2122,28 +2166,24 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>93</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B37" s="6"/>
       <c r="C37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" s="4">
-        <v>4774</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D37" s="4"/>
       <c r="E37" s="7" t="str">
-        <f>IF(D37&gt;0,HYPERLINK(_xlfn.CONCAT(H37,D37),IF(B37="",C37,B37)),"")</f>
-        <v>M Dahlberg</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="F37" s="7" t="str">
-        <f>IF(D37&gt;0,HYPERLINK(_xlfn.CONCAT(I37,D37),IF(B37="",C37,B37)),"")</f>
-        <v>M Dahlberg</v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="G37" s="7" t="str">
-        <f>IF(D37&gt;0,HYPERLINK(_xlfn.CONCAT(J37,D37),IF(B37="",C37,B37)),"")</f>
-        <v>M Dahlberg</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="H37" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2162,28 +2202,24 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>7</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B38" s="6"/>
       <c r="C38" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="4">
-        <v>494474</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="7" t="str">
-        <f>IF(D38&gt;0,HYPERLINK(_xlfn.CONCAT(H38,D38),IF(B38="",C38,B38)),"")</f>
-        <v>Räkan</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="F38" s="7" t="str">
-        <f>IF(D38&gt;0,HYPERLINK(_xlfn.CONCAT(I38,D38),IF(B38="",C38,B38)),"")</f>
-        <v>Räkan</v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="G38" s="7" t="str">
-        <f>IF(D38&gt;0,HYPERLINK(_xlfn.CONCAT(J38,D38),IF(B38="",C38,B38)),"")</f>
-        <v>Räkan</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="H38" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2202,53 +2238,68 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5" t="s">
-        <v>85</v>
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="D39" s="4">
-        <v>483871</v>
+        <v>4774</v>
       </c>
       <c r="E39" s="7" t="str">
-        <f>IF(D39&gt;0,HYPERLINK(_xlfn.CONCAT(H39,D39),IF(B39="",C39,B39)),"")</f>
-        <v>Mattias Berggren</v>
+        <f t="shared" si="3"/>
+        <v>M Dahlberg</v>
       </c>
       <c r="F39" s="7" t="str">
-        <f>IF(D39&gt;0,HYPERLINK(_xlfn.CONCAT(I39,D39),IF(B39="",C39,B39)),"")</f>
-        <v>Mattias Berggren</v>
+        <f t="shared" si="4"/>
+        <v>M Dahlberg</v>
       </c>
       <c r="G39" s="7" t="str">
-        <f>IF(D39&gt;0,HYPERLINK(_xlfn.CONCAT(J39,D39),IF(B39="",C39,B39)),"")</f>
-        <v>Mattias Berggren</v>
-      </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
+        <f t="shared" si="5"/>
+        <v>M Dahlberg</v>
+      </c>
+      <c r="H39" s="4" t="str">
+        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+      </c>
+      <c r="I39" s="4" t="str">
+        <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="J39" s="4" t="str">
+        <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="4">
+        <v>494474</v>
+      </c>
       <c r="E40" s="7" t="str">
-        <f>IF(D40&gt;0,HYPERLINK(_xlfn.CONCAT(H40,D40),IF(B40="",C40,B40)),"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>Räkan</v>
       </c>
       <c r="F40" s="7" t="str">
-        <f>IF(D40&gt;0,HYPERLINK(_xlfn.CONCAT(I40,D40),IF(B40="",C40,B40)),"")</f>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>Räkan</v>
       </c>
       <c r="G40" s="7" t="str">
-        <f>IF(D40&gt;0,HYPERLINK(_xlfn.CONCAT(J40,D40),IF(B40="",C40,B40)),"")</f>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>Räkan</v>
       </c>
       <c r="H40" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2267,28 +2318,26 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>12</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B41" s="6"/>
       <c r="C41" s="5" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D41" s="4">
-        <v>26370</v>
+        <v>483871</v>
       </c>
       <c r="E41" s="7" t="str">
-        <f>IF(D41&gt;0,HYPERLINK(_xlfn.CONCAT(H41,D41),IF(B41="",C41,B41)),"")</f>
-        <v>Mogge</v>
+        <f t="shared" si="3"/>
+        <v>Mattias Berggren</v>
       </c>
       <c r="F41" s="7" t="str">
-        <f>IF(D41&gt;0,HYPERLINK(_xlfn.CONCAT(I41,D41),IF(B41="",C41,B41)),"")</f>
-        <v>Mogge</v>
+        <f t="shared" si="4"/>
+        <v>Mattias Berggren</v>
       </c>
       <c r="G41" s="7" t="str">
-        <f>IF(D41&gt;0,HYPERLINK(_xlfn.CONCAT(J41,D41),IF(B41="",C41,B41)),"")</f>
-        <v>Mogge</v>
+        <f t="shared" si="5"/>
+        <v>Mattias Berggren</v>
       </c>
       <c r="H41" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2307,28 +2356,24 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="4">
-        <v>449191</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="7" t="str">
-        <f>IF(D42&gt;0,HYPERLINK(_xlfn.CONCAT(H42,D42),IF(B42="",C42,B42)),"")</f>
-        <v>Örjan</v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="F42" s="7" t="str">
-        <f>IF(D42&gt;0,HYPERLINK(_xlfn.CONCAT(I42,D42),IF(B42="",C42,B42)),"")</f>
-        <v>Örjan</v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="G42" s="7" t="str">
-        <f>IF(D42&gt;0,HYPERLINK(_xlfn.CONCAT(J42,D42),IF(B42="",C42,B42)),"")</f>
-        <v>Örjan</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="H42" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2347,28 +2392,28 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D43" s="4">
-        <v>4642</v>
+        <v>26370</v>
       </c>
       <c r="E43" s="7" t="str">
-        <f>IF(D43&gt;0,HYPERLINK(_xlfn.CONCAT(H43,D43),IF(B43="",C43,B43)),"")</f>
-        <v>Ove</v>
+        <f t="shared" si="3"/>
+        <v>Mogge</v>
       </c>
       <c r="F43" s="7" t="str">
-        <f>IF(D43&gt;0,HYPERLINK(_xlfn.CONCAT(I43,D43),IF(B43="",C43,B43)),"")</f>
-        <v>Ove</v>
+        <f t="shared" si="4"/>
+        <v>Mogge</v>
       </c>
       <c r="G43" s="7" t="str">
-        <f>IF(D43&gt;0,HYPERLINK(_xlfn.CONCAT(J43,D43),IF(B43="",C43,B43)),"")</f>
-        <v>Ove</v>
+        <f t="shared" si="5"/>
+        <v>Mogge</v>
       </c>
       <c r="H43" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2387,28 +2432,28 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>58</v>
+        <v>2</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="D44" s="4">
-        <v>25129</v>
+        <v>449191</v>
       </c>
       <c r="E44" s="7" t="str">
-        <f>IF(D44&gt;0,HYPERLINK(_xlfn.CONCAT(H44,D44),IF(B44="",C44,B44)),"")</f>
-        <v>Ungtuppen</v>
+        <f t="shared" si="3"/>
+        <v>Örjan</v>
       </c>
       <c r="F44" s="7" t="str">
-        <f>IF(D44&gt;0,HYPERLINK(_xlfn.CONCAT(I44,D44),IF(B44="",C44,B44)),"")</f>
-        <v>Ungtuppen</v>
+        <f t="shared" si="4"/>
+        <v>Örjan</v>
       </c>
       <c r="G44" s="7" t="str">
-        <f>IF(D44&gt;0,HYPERLINK(_xlfn.CONCAT(J44,D44),IF(B44="",C44,B44)),"")</f>
-        <v>Ungtuppen</v>
+        <f t="shared" si="5"/>
+        <v>Örjan</v>
       </c>
       <c r="H44" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2427,28 +2472,28 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>59</v>
+        <v>13</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="D45" s="4">
-        <v>24134</v>
+        <v>4642</v>
       </c>
       <c r="E45" s="7" t="str">
-        <f>IF(D45&gt;0,HYPERLINK(_xlfn.CONCAT(H45,D45),IF(B45="",C45,B45)),"")</f>
-        <v>Ultraräkan</v>
+        <f t="shared" si="3"/>
+        <v>Ove</v>
       </c>
       <c r="F45" s="7" t="str">
-        <f>IF(D45&gt;0,HYPERLINK(_xlfn.CONCAT(I45,D45),IF(B45="",C45,B45)),"")</f>
-        <v>Ultraräkan</v>
+        <f t="shared" si="4"/>
+        <v>Ove</v>
       </c>
       <c r="G45" s="7" t="str">
-        <f>IF(D45&gt;0,HYPERLINK(_xlfn.CONCAT(J45,D45),IF(B45="",C45,B45)),"")</f>
-        <v>Ultraräkan</v>
+        <f t="shared" si="5"/>
+        <v>Ove</v>
       </c>
       <c r="H45" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2467,26 +2512,28 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>45</v>
-      </c>
-      <c r="B46" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="C46" s="5" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="D46" s="4">
-        <v>473617</v>
+        <v>25129</v>
       </c>
       <c r="E46" s="7" t="str">
-        <f>IF(D46&gt;0,HYPERLINK(_xlfn.CONCAT(H46,D46),IF(B46="",C46,B46)),"")</f>
-        <v>Peter Windeman</v>
+        <f t="shared" si="3"/>
+        <v>Ungtuppen</v>
       </c>
       <c r="F46" s="7" t="str">
-        <f>IF(D46&gt;0,HYPERLINK(_xlfn.CONCAT(I46,D46),IF(B46="",C46,B46)),"")</f>
-        <v>Peter Windeman</v>
+        <f t="shared" si="4"/>
+        <v>Ungtuppen</v>
       </c>
       <c r="G46" s="7" t="str">
-        <f>IF(D46&gt;0,HYPERLINK(_xlfn.CONCAT(J46,D46),IF(B46="",C46,B46)),"")</f>
-        <v>Peter Windeman</v>
+        <f t="shared" si="5"/>
+        <v>Ungtuppen</v>
       </c>
       <c r="H46" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2505,26 +2552,28 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D47" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="D47" s="4">
+        <v>24134</v>
+      </c>
       <c r="E47" s="7" t="str">
-        <f>IF(D47&gt;0,HYPERLINK(_xlfn.CONCAT(H47,D47),IF(B47="",C47,B47)),"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>Ultraräkan</v>
       </c>
       <c r="F47" s="7" t="str">
-        <f>IF(D47&gt;0,HYPERLINK(_xlfn.CONCAT(I47,D47),IF(B47="",C47,B47)),"")</f>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>Ultraräkan</v>
       </c>
       <c r="G47" s="7" t="str">
-        <f>IF(D47&gt;0,HYPERLINK(_xlfn.CONCAT(J47,D47),IF(B47="",C47,B47)),"")</f>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>Ultraräkan</v>
       </c>
       <c r="H47" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2543,24 +2592,26 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="D48" s="4">
+        <v>473617</v>
+      </c>
       <c r="E48" s="7" t="str">
-        <f>IF(D48&gt;0,HYPERLINK(_xlfn.CONCAT(H48,D48),IF(B48="",C48,B48)),"")</f>
-        <v/>
+        <f t="shared" si="3"/>
+        <v>Peter Windeman</v>
       </c>
       <c r="F48" s="7" t="str">
-        <f>IF(D48&gt;0,HYPERLINK(_xlfn.CONCAT(I48,D48),IF(B48="",C48,B48)),"")</f>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>Peter Windeman</v>
       </c>
       <c r="G48" s="7" t="str">
-        <f>IF(D48&gt;0,HYPERLINK(_xlfn.CONCAT(J48,D48),IF(B48="",C48,B48)),"")</f>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>Peter Windeman</v>
       </c>
       <c r="H48" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
@@ -2579,21 +2630,25 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>48</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="D49" s="4"/>
       <c r="E49" s="7" t="str">
-        <f>IF(D49&gt;0,HYPERLINK(_xlfn.CONCAT(H49,D49),IF(B49="",C49,B49)),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="F49" s="7" t="str">
-        <f>IF(D49&gt;0,HYPERLINK(_xlfn.CONCAT(I49,D49),IF(B49="",C49,B49)),"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G49" s="7" t="str">
-        <f>IF(D49&gt;0,HYPERLINK(_xlfn.CONCAT(J49,D49),IF(B49="",C49,B49)),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="H49" s="4" t="str">
@@ -2613,23 +2668,20 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>49</v>
-      </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="7" t="str">
-        <f>IF(D50&gt;0,HYPERLINK(_xlfn.CONCAT(H50,D50),IF(B50="",C50,B50)),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="7" t="str">
-        <f>IF(D50&gt;0,HYPERLINK(_xlfn.CONCAT(I50,D50),IF(B50="",C50,B50)),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="7" t="str">
-        <f>IF(D50&gt;0,HYPERLINK(_xlfn.CONCAT(J50,D50),IF(B50="",C50,B50)),"")</f>
-        <v/>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="4">
+        <v>26404</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
       <c r="H50" s="4" t="str">
         <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
         <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
@@ -2645,10 +2697,114 @@
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
     </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="7" t="str">
+        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(H51,D51),IF(B51="",C51,B51)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="7" t="str">
+        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(I51,D51),IF(B51="",C51,B51)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="7" t="str">
+        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(J51,D51),IF(B51="",C51,B51)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="4" t="str">
+        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+      </c>
+      <c r="I51" s="4" t="str">
+        <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="J51" s="4" t="str">
+        <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>50</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="7" t="str">
+        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(H52,D52),IF(B52="",C52,B52)),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="7" t="str">
+        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(I52,D52),IF(B52="",C52,B52)),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="7" t="str">
+        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(J52,D52),IF(B52="",C52,B52)),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="4" t="str">
+        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+      </c>
+      <c r="I52" s="4" t="str">
+        <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="J52" s="4" t="str">
+        <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="7" t="str">
+        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(H53,D53),IF(B53="",C53,B53)),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="7" t="str">
+        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(I53,D53),IF(B53="",C53,B53)),"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="7" t="str">
+        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(J53,D53),IF(B53="",C53,B53)),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="4" t="str">
+        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+      </c>
+      <c r="I53" s="4" t="str">
+        <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="J53" s="4" t="str">
+        <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L50">
-      <sortCondition ref="C1"/>
+  <autoFilter ref="A1:L53" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L53">
+      <sortCondition ref="C1:C53"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2657,11 +2813,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E8E445-90B6-496D-AEB6-772532BC7A87}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2694,7 +2851,7 @@
       <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2705,7 +2862,7 @@
       <c r="B4" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" t="s">
         <v>69</v>
       </c>
     </row>

--- a/KoF/GPS-Speedsurfing-Users.xlsx
+++ b/KoF/GPS-Speedsurfing-Users.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\KoF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D82DDD3-64DA-4BC0-91B2-AD33CDAC2856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94ABD958-D3F5-49B6-8E98-DCA852136FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
     <sheet name="BaseUrl" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">User!$A$1:$L$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">User!$A$1:$M$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>BQ</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Henrik Larsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL Sessions </t>
   </si>
 </sst>
 </file>
@@ -447,7 +450,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -467,6 +470,10 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -750,23 +757,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M53"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="44.33203125" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="58.109375" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="56.109375" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="48.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="76.85546875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="58.140625" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="56.140625" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="48.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -788,17 +796,20 @@
       <c r="G1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -812,33 +823,37 @@
         <v>2558</v>
       </c>
       <c r="E2" s="7" t="str">
-        <f t="shared" ref="E2:E22" si="0">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(H2,D2),IF(B2="",C2,B2)),"")</f>
+        <f t="shared" ref="E2:E22" si="0">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(I2,D2),IF(B2="",C2,B2)),"")</f>
         <v>BQ</v>
       </c>
       <c r="F2" s="7" t="str">
-        <f t="shared" ref="F2:F22" si="1">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(I2,D2),IF(B2="",C2,B2)),"")</f>
+        <f t="shared" ref="F2:F22" si="1">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(J2,D2),IF(B2="",C2,B2)),"")</f>
         <v>BQ</v>
       </c>
       <c r="G2" s="7" t="str">
-        <f t="shared" ref="G2:G22" si="2">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(J2,D2),IF(B2="",C2,B2)),"")</f>
+        <f t="shared" ref="G2:G22" si="2">IF(D2&gt;0,HYPERLINK(_xlfn.CONCAT(K2,D2),IF(B2="",C2,B2)),"")</f>
         <v>BQ</v>
       </c>
       <c r="H2" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f>IF(D2&gt;0,_xlfn.CONCAT(K2,D2),"_")</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=2558</v>
       </c>
       <c r="I2" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J2" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K2" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K2" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -864,21 +879,25 @@
         <v>AN</v>
       </c>
       <c r="H3" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" ref="H3:H53" si="3">IF(D3&gt;0,_xlfn.CONCAT(K3,D3),"_")</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=25610</v>
       </c>
       <c r="I3" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J3" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K3" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K3" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L3" s="4"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -904,21 +923,25 @@
         <v>Arne</v>
       </c>
       <c r="H4" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=497225</v>
       </c>
       <c r="I4" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J4" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K4" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K4" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -944,21 +967,25 @@
         <v>AT</v>
       </c>
       <c r="H5" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=469015</v>
       </c>
       <c r="I5" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J5" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K5" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K5" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -984,21 +1011,25 @@
         <v>J&amp;B</v>
       </c>
       <c r="H6" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=22378</v>
       </c>
       <c r="I6" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J6" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K6" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K6" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1024,21 +1055,25 @@
         <v>Berra</v>
       </c>
       <c r="H7" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=23841</v>
       </c>
       <c r="I7" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J7" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K7" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K7" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1060,21 +1095,25 @@
         <v/>
       </c>
       <c r="H8" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I8" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J8" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K8" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K8" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1096,21 +1135,25 @@
         <v/>
       </c>
       <c r="H9" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I9" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J9" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K9" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K9" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1136,21 +1179,25 @@
         <v>Borgelind</v>
       </c>
       <c r="H10" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=587</v>
       </c>
       <c r="I10" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J10" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K10" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K10" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1176,21 +1223,25 @@
         <v>EA</v>
       </c>
       <c r="H11" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=4051</v>
       </c>
       <c r="I11" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J11" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K11" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K11" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1216,21 +1267,25 @@
         <v>Grimberg</v>
       </c>
       <c r="H12" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=27753</v>
       </c>
       <c r="I12" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J12" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K12" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K12" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1252,21 +1307,25 @@
         <v/>
       </c>
       <c r="H13" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I13" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J13" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K13" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K13" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L13" s="4"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1292,21 +1351,25 @@
         <v>Budda</v>
       </c>
       <c r="H14" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=1007</v>
       </c>
       <c r="I14" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J14" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K14" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K14" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1314,35 +1377,41 @@
       <c r="C15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>25706</v>
+      </c>
       <c r="E15" s="7" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>David Giaina</v>
       </c>
       <c r="F15" s="7" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>David Giaina</v>
       </c>
       <c r="G15" s="7" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>David Giaina</v>
       </c>
       <c r="H15" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=25706</v>
       </c>
       <c r="I15" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J15" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K15" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K15" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1368,21 +1437,25 @@
         <v>djong1</v>
       </c>
       <c r="H16" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=53</v>
       </c>
       <c r="I16" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J16" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K16" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K16" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -1408,21 +1481,25 @@
         <v>E Larsson</v>
       </c>
       <c r="H17" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=713</v>
       </c>
       <c r="I17" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J17" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K17" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K17" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -1446,21 +1523,25 @@
         <v/>
       </c>
       <c r="H18" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I18" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J18" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K18" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K18" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L18" s="4"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -1486,21 +1567,25 @@
         <v>Plettil</v>
       </c>
       <c r="H19" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=18200</v>
       </c>
       <c r="I19" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J19" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K19" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K19" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L19" s="4"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -1522,21 +1607,25 @@
         <v/>
       </c>
       <c r="H20" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I20" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J20" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K20" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K20" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L20" s="4"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -1562,21 +1651,25 @@
         <v>Harald</v>
       </c>
       <c r="H21" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=26470</v>
       </c>
       <c r="I21" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J21" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K21" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K21" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="6" t="s">
         <v>98</v>
@@ -1600,21 +1693,25 @@
         <v>Henke Torslanda</v>
       </c>
       <c r="H22" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=27859</v>
       </c>
       <c r="I22" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J22" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K22" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K22" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -1624,33 +1721,37 @@
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="7" t="str">
-        <f t="shared" ref="E23:E49" si="3">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(H23,D23),IF(B23="",C23,B23)),"")</f>
+        <f t="shared" ref="E23:E49" si="4">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(I23,D23),IF(B23="",C23,B23)),"")</f>
         <v/>
       </c>
       <c r="F23" s="7" t="str">
-        <f t="shared" ref="F23:F49" si="4">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(I23,D23),IF(B23="",C23,B23)),"")</f>
+        <f t="shared" ref="F23:F49" si="5">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(J23,D23),IF(B23="",C23,B23)),"")</f>
         <v/>
       </c>
       <c r="G23" s="7" t="str">
-        <f t="shared" ref="G23:G49" si="5">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(J23,D23),IF(B23="",C23,B23)),"")</f>
+        <f t="shared" ref="G23:G49" si="6">IF(D23&gt;0,HYPERLINK(_xlfn.CONCAT(K23,D23),IF(B23="",C23,B23)),"")</f>
         <v/>
       </c>
       <c r="H23" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I23" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J23" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K23" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K23" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L23" s="4"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -1664,33 +1765,37 @@
         <v>495257</v>
       </c>
       <c r="E24" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>JesPer</v>
-      </c>
-      <c r="F24" s="7" t="str">
         <f t="shared" si="4"/>
         <v>JesPer</v>
       </c>
-      <c r="G24" s="7" t="str">
+      <c r="F24" s="7" t="str">
         <f t="shared" si="5"/>
         <v>JesPer</v>
       </c>
+      <c r="G24" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>JesPer</v>
+      </c>
       <c r="H24" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=495257</v>
       </c>
       <c r="I24" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J24" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K24" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K24" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L24" s="4"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -1704,33 +1809,37 @@
         <v>26191</v>
       </c>
       <c r="E25" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Jocke</v>
-      </c>
-      <c r="F25" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Jocke</v>
       </c>
-      <c r="G25" s="7" t="str">
+      <c r="F25" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Jocke</v>
       </c>
+      <c r="G25" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Jocke</v>
+      </c>
       <c r="H25" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=26191</v>
       </c>
       <c r="I25" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J25" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K25" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K25" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L25" s="4"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -1742,33 +1851,37 @@
         <v>604</v>
       </c>
       <c r="E26" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Johan Gelander</v>
-      </c>
-      <c r="F26" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Johan Gelander</v>
       </c>
-      <c r="G26" s="7" t="str">
+      <c r="F26" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Johan Gelander</v>
       </c>
+      <c r="G26" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Johan Gelander</v>
+      </c>
       <c r="H26" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=604</v>
       </c>
       <c r="I26" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J26" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K26" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K26" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -1782,33 +1895,37 @@
         <v>470910</v>
       </c>
       <c r="E27" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Millbergs</v>
-      </c>
-      <c r="F27" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Millbergs</v>
       </c>
-      <c r="G27" s="7" t="str">
+      <c r="F27" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Millbergs</v>
       </c>
+      <c r="G27" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Millbergs</v>
+      </c>
       <c r="H27" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=470910</v>
       </c>
       <c r="I27" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J27" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K27" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K27" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M27" s="4"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -1822,33 +1939,37 @@
         <v>6195</v>
       </c>
       <c r="E28" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Joko</v>
-      </c>
-      <c r="F28" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Joko</v>
       </c>
-      <c r="G28" s="7" t="str">
+      <c r="F28" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Joko</v>
       </c>
+      <c r="G28" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Joko</v>
+      </c>
       <c r="H28" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=6195</v>
       </c>
       <c r="I28" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J28" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K28" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K28" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M28" s="4"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -1862,33 +1983,37 @@
         <v>469112</v>
       </c>
       <c r="E29" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Bergström</v>
-      </c>
-      <c r="F29" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Bergström</v>
       </c>
-      <c r="G29" s="7" t="str">
+      <c r="F29" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Bergström</v>
       </c>
+      <c r="G29" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Bergström</v>
+      </c>
       <c r="H29" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=469112</v>
       </c>
       <c r="I29" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J29" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K29" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K29" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L29" s="4"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M29" s="4"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -1902,33 +2027,37 @@
         <v>26663</v>
       </c>
       <c r="E30" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Göran</v>
-      </c>
-      <c r="F30" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Göran</v>
       </c>
-      <c r="G30" s="7" t="str">
+      <c r="F30" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Göran</v>
       </c>
+      <c r="G30" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Göran</v>
+      </c>
       <c r="H30" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=26663</v>
       </c>
       <c r="I30" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J30" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K30" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K30" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L30" s="4"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -1939,36 +2068,40 @@
         <v>46</v>
       </c>
       <c r="D31" s="4">
-        <v>494504</v>
+        <v>26641</v>
       </c>
       <c r="E31" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Sören</v>
-      </c>
-      <c r="F31" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Sören</v>
       </c>
-      <c r="G31" s="7" t="str">
+      <c r="F31" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Sören</v>
       </c>
+      <c r="G31" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Sören</v>
+      </c>
       <c r="H31" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=26641</v>
       </c>
       <c r="I31" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J31" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K31" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K31" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L31" s="4"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -1982,33 +2115,37 @@
         <v>469141</v>
       </c>
       <c r="E32" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Kate</v>
-      </c>
-      <c r="F32" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Kate</v>
       </c>
-      <c r="G32" s="7" t="str">
+      <c r="F32" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Kate</v>
       </c>
+      <c r="G32" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Kate</v>
+      </c>
       <c r="H32" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=469141</v>
       </c>
       <c r="I32" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J32" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K32" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K32" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L32" s="4"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -2020,33 +2157,37 @@
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F33" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G33" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H33" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I33" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J33" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K33" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K33" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L33" s="4"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -2060,33 +2201,37 @@
         <v>2250</v>
       </c>
       <c r="E34" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Richardsson</v>
-      </c>
-      <c r="F34" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Richardsson</v>
       </c>
-      <c r="G34" s="7" t="str">
+      <c r="F34" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Richardsson</v>
       </c>
+      <c r="G34" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Richardsson</v>
+      </c>
       <c r="H34" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=2250</v>
       </c>
       <c r="I34" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J34" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K34" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K34" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L34" s="4"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -2098,33 +2243,37 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F35" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G35" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H35" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I35" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J35" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K35" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K35" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L35" s="4"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -2138,33 +2287,37 @@
         <v>48391</v>
       </c>
       <c r="E36" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Distner</v>
-      </c>
-      <c r="F36" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Distner</v>
       </c>
-      <c r="G36" s="7" t="str">
+      <c r="F36" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Distner</v>
       </c>
+      <c r="G36" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Distner</v>
+      </c>
       <c r="H36" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=48391</v>
       </c>
       <c r="I36" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J36" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K36" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K36" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L36" s="4"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -2174,33 +2327,37 @@
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F37" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G37" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H37" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I37" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J37" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K37" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K37" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L37" s="4"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -2210,33 +2367,37 @@
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F38" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G38" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H38" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I38" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J38" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K38" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K38" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L38" s="4"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -2250,33 +2411,37 @@
         <v>4774</v>
       </c>
       <c r="E39" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>M Dahlberg</v>
-      </c>
-      <c r="F39" s="7" t="str">
         <f t="shared" si="4"/>
         <v>M Dahlberg</v>
       </c>
-      <c r="G39" s="7" t="str">
+      <c r="F39" s="7" t="str">
         <f t="shared" si="5"/>
         <v>M Dahlberg</v>
       </c>
+      <c r="G39" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>M Dahlberg</v>
+      </c>
       <c r="H39" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=4774</v>
       </c>
       <c r="I39" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J39" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K39" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K39" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L39" s="4"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -2290,33 +2455,37 @@
         <v>494474</v>
       </c>
       <c r="E40" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Räkan</v>
-      </c>
-      <c r="F40" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Räkan</v>
       </c>
-      <c r="G40" s="7" t="str">
+      <c r="F40" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Räkan</v>
       </c>
+      <c r="G40" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Räkan</v>
+      </c>
       <c r="H40" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=494474</v>
       </c>
       <c r="I40" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J40" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K40" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K40" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L40" s="4"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -2328,33 +2497,37 @@
         <v>483871</v>
       </c>
       <c r="E41" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Mattias Berggren</v>
-      </c>
-      <c r="F41" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Mattias Berggren</v>
       </c>
-      <c r="G41" s="7" t="str">
+      <c r="F41" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Mattias Berggren</v>
       </c>
+      <c r="G41" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Mattias Berggren</v>
+      </c>
       <c r="H41" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=483871</v>
       </c>
       <c r="I41" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J41" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K41" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K41" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L41" s="4"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -2364,33 +2537,37 @@
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F42" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G42" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H42" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I42" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J42" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K42" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K42" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L42" s="4"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -2404,33 +2581,37 @@
         <v>26370</v>
       </c>
       <c r="E43" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Mogge</v>
-      </c>
-      <c r="F43" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Mogge</v>
       </c>
-      <c r="G43" s="7" t="str">
+      <c r="F43" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Mogge</v>
       </c>
+      <c r="G43" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Mogge</v>
+      </c>
       <c r="H43" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=26370</v>
       </c>
       <c r="I43" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J43" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K43" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K43" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L43" s="4"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -2444,33 +2625,37 @@
         <v>449191</v>
       </c>
       <c r="E44" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Örjan</v>
-      </c>
-      <c r="F44" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Örjan</v>
       </c>
-      <c r="G44" s="7" t="str">
+      <c r="F44" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Örjan</v>
       </c>
+      <c r="G44" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Örjan</v>
+      </c>
       <c r="H44" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=449191</v>
       </c>
       <c r="I44" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J44" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K44" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K44" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L44" s="4"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -2484,33 +2669,37 @@
         <v>4642</v>
       </c>
       <c r="E45" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Ove</v>
-      </c>
-      <c r="F45" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Ove</v>
       </c>
-      <c r="G45" s="7" t="str">
+      <c r="F45" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Ove</v>
       </c>
+      <c r="G45" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Ove</v>
+      </c>
       <c r="H45" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=4642</v>
       </c>
       <c r="I45" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J45" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K45" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K45" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L45" s="4"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -2524,33 +2713,37 @@
         <v>25129</v>
       </c>
       <c r="E46" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Ungtuppen</v>
-      </c>
-      <c r="F46" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Ungtuppen</v>
       </c>
-      <c r="G46" s="7" t="str">
+      <c r="F46" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Ungtuppen</v>
       </c>
+      <c r="G46" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Ungtuppen</v>
+      </c>
       <c r="H46" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=25129</v>
       </c>
       <c r="I46" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J46" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K46" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K46" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L46" s="4"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -2564,33 +2757,37 @@
         <v>24134</v>
       </c>
       <c r="E47" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Ultraräkan</v>
-      </c>
-      <c r="F47" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Ultraräkan</v>
       </c>
-      <c r="G47" s="7" t="str">
+      <c r="F47" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Ultraräkan</v>
       </c>
+      <c r="G47" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Ultraräkan</v>
+      </c>
       <c r="H47" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=24134</v>
       </c>
       <c r="I47" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J47" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K47" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K47" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L47" s="4"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -2602,33 +2799,37 @@
         <v>473617</v>
       </c>
       <c r="E48" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>Peter Windeman</v>
-      </c>
-      <c r="F48" s="7" t="str">
         <f t="shared" si="4"/>
         <v>Peter Windeman</v>
       </c>
-      <c r="G48" s="7" t="str">
+      <c r="F48" s="7" t="str">
         <f t="shared" si="5"/>
         <v>Peter Windeman</v>
       </c>
+      <c r="G48" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Peter Windeman</v>
+      </c>
       <c r="H48" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=473617</v>
       </c>
       <c r="I48" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J48" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K48" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K48" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L48" s="4"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M48" s="4"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -2640,33 +2841,37 @@
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F49" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G49" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H49" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I49" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J49" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K49" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K49" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L49" s="4"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M49" s="4"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -2683,21 +2888,25 @@
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=26404</v>
       </c>
       <c r="I50" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J50" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K50" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K50" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L50" s="4"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -2707,33 +2916,37 @@
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="7" t="str">
-        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(H51,D51),IF(B51="",C51,B51)),"")</f>
+        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(I51,D51),IF(B51="",C51,B51)),"")</f>
         <v/>
       </c>
       <c r="F51" s="7" t="str">
-        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(I51,D51),IF(B51="",C51,B51)),"")</f>
+        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(J51,D51),IF(B51="",C51,B51)),"")</f>
         <v/>
       </c>
       <c r="G51" s="7" t="str">
-        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(J51,D51),IF(B51="",C51,B51)),"")</f>
+        <f>IF(D51&gt;0,HYPERLINK(_xlfn.CONCAT(K51,D51),IF(B51="",C51,B51)),"")</f>
         <v/>
       </c>
       <c r="H51" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I51" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J51" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K51" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K51" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L51" s="4"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -2741,33 +2954,37 @@
       <c r="C52" s="5"/>
       <c r="D52" s="4"/>
       <c r="E52" s="7" t="str">
-        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(H52,D52),IF(B52="",C52,B52)),"")</f>
+        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(I52,D52),IF(B52="",C52,B52)),"")</f>
         <v/>
       </c>
       <c r="F52" s="7" t="str">
-        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(I52,D52),IF(B52="",C52,B52)),"")</f>
+        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(J52,D52),IF(B52="",C52,B52)),"")</f>
         <v/>
       </c>
       <c r="G52" s="7" t="str">
-        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(J52,D52),IF(B52="",C52,B52)),"")</f>
+        <f>IF(D52&gt;0,HYPERLINK(_xlfn.CONCAT(K52,D52),IF(B52="",C52,B52)),"")</f>
         <v/>
       </c>
       <c r="H52" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I52" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J52" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K52" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K52" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L52" s="4"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M52" s="4"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -2775,35 +2992,39 @@
       <c r="C53" s="5"/>
       <c r="D53" s="4"/>
       <c r="E53" s="7" t="str">
-        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(H53,D53),IF(B53="",C53,B53)),"")</f>
+        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(I53,D53),IF(B53="",C53,B53)),"")</f>
         <v/>
       </c>
       <c r="F53" s="7" t="str">
-        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(I53,D53),IF(B53="",C53,B53)),"")</f>
+        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(J53,D53),IF(B53="",C53,B53)),"")</f>
         <v/>
       </c>
       <c r="G53" s="7" t="str">
-        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(J53,D53),IF(B53="",C53,B53)),"")</f>
+        <f>IF(D53&gt;0,HYPERLINK(_xlfn.CONCAT(K53,D53),IF(B53="",C53,B53)),"")</f>
         <v/>
       </c>
       <c r="H53" s="4" t="str">
-        <f>_xlfn.XLOOKUP($H$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
+        <f t="shared" si="3"/>
+        <v>_</v>
       </c>
       <c r="I53" s="4" t="str">
         <f>_xlfn.XLOOKUP($I$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+        <v>https://www.gps-speedsurfing.com/UserDetails?Id=</v>
       </c>
       <c r="J53" s="4" t="str">
         <f>_xlfn.XLOOKUP($J$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
-        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
-      </c>
-      <c r="K53" s="4"/>
+        <v>https://www.gps-speedsurfing.com/sessions/userequipment?userid=</v>
+      </c>
+      <c r="K53" s="4" t="str">
+        <f>_xlfn.XLOOKUP($K$1,BaseUrl!$B:$B,BaseUrl!$C:$C,"",0)</f>
+        <v>https://www.gps-speedsurfing.com/sessions/usersessions?userid=</v>
+      </c>
       <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L53" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L53">
+  <autoFilter ref="A1:M53" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M53">
       <sortCondition ref="C1:C53"/>
     </sortState>
   </autoFilter>
@@ -2815,14 +3036,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E8E445-90B6-496D-AEB6-772532BC7A87}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -2833,7 +3054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2844,7 +3065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -2855,7 +3076,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
